--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/132.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/132.xlsx
@@ -426,13 +426,13 @@
         <v>-16.42539113520136</v>
       </c>
       <c r="E2">
-        <v>-20.64204099096922</v>
+        <v>-20.0701852932806</v>
       </c>
       <c r="F2">
-        <v>-5.010462391453195</v>
+        <v>-6.137581326439745</v>
       </c>
       <c r="G2">
-        <v>-15.76777201529876</v>
+        <v>-14.99448485659918</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-16.29857581099774</v>
       </c>
       <c r="E3">
-        <v>-20.71726347271063</v>
+        <v>-20.60782384136726</v>
       </c>
       <c r="F3">
-        <v>-5.438068958247911</v>
+        <v>-6.368120116475861</v>
       </c>
       <c r="G3">
-        <v>-14.78223088462157</v>
+        <v>-14.8290999330938</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.15947677951992</v>
       </c>
       <c r="E4">
-        <v>-22.18533587583526</v>
+        <v>-21.49466207713339</v>
       </c>
       <c r="F4">
-        <v>-5.206250340574469</v>
+        <v>-6.276980649717651</v>
       </c>
       <c r="G4">
-        <v>-15.64783922677481</v>
+        <v>-14.51881243133453</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.01469056546</v>
       </c>
       <c r="E5">
-        <v>-22.17963905553361</v>
+        <v>-22.1755000302906</v>
       </c>
       <c r="F5">
-        <v>-4.990888898092445</v>
+        <v>-6.316760094951188</v>
       </c>
       <c r="G5">
-        <v>-14.25557605805215</v>
+        <v>-14.00993192376546</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-15.86512392903444</v>
       </c>
       <c r="E6">
-        <v>-21.21397820118997</v>
+        <v>-23.3184325281385</v>
       </c>
       <c r="F6">
-        <v>-5.004436846965231</v>
+        <v>-5.821159060816181</v>
       </c>
       <c r="G6">
-        <v>-14.05536750601919</v>
+        <v>-14.20475090766049</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.69394565941663</v>
       </c>
       <c r="E7">
-        <v>-24.38522326402144</v>
+        <v>-23.45022923565774</v>
       </c>
       <c r="F7">
-        <v>-5.207003326543614</v>
+        <v>-5.965937802007867</v>
       </c>
       <c r="G7">
-        <v>-14.13829005068686</v>
+        <v>-14.07241516027367</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.49148469864253</v>
       </c>
       <c r="E8">
-        <v>-23.04954532698506</v>
+        <v>-23.24241303497174</v>
       </c>
       <c r="F8">
-        <v>-5.340619816982577</v>
+        <v>-5.902839400201824</v>
       </c>
       <c r="G8">
-        <v>-14.41609944543311</v>
+        <v>-14.07920177862917</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.24089893353765</v>
       </c>
       <c r="E9">
-        <v>-23.84167958582878</v>
+        <v>-23.97291476257107</v>
       </c>
       <c r="F9">
-        <v>-5.35781258242768</v>
+        <v>-6.27885027494577</v>
       </c>
       <c r="G9">
-        <v>-15.26519478643646</v>
+        <v>-13.9025328606532</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.90476388600971</v>
       </c>
       <c r="E10">
-        <v>-23.54944357269179</v>
+        <v>-25.20183845335063</v>
       </c>
       <c r="F10">
-        <v>-5.280795951519799</v>
+        <v>-6.281860976271244</v>
       </c>
       <c r="G10">
-        <v>-14.64732118807796</v>
+        <v>-13.23510536139012</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-14.46747749297544</v>
       </c>
       <c r="E11">
-        <v>-25.55992753550716</v>
+        <v>-24.90539095938651</v>
       </c>
       <c r="F11">
-        <v>-5.26639478422213</v>
+        <v>-6.294741675201076</v>
       </c>
       <c r="G11">
-        <v>-13.34411500490724</v>
+        <v>-13.46721764078504</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-13.91859108579768</v>
       </c>
       <c r="E12">
-        <v>-25.80485005221201</v>
+        <v>-25.26066333071027</v>
       </c>
       <c r="F12">
-        <v>-5.48172557711025</v>
+        <v>-6.271949146113047</v>
       </c>
       <c r="G12">
-        <v>-12.75720493897755</v>
+        <v>-13.4907589301148</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-13.24834186072353</v>
       </c>
       <c r="E13">
-        <v>-27.13520703228938</v>
+        <v>-26.32021303665494</v>
       </c>
       <c r="F13">
-        <v>-4.805959188887067</v>
+        <v>-6.139502310446836</v>
       </c>
       <c r="G13">
-        <v>-11.80296005055587</v>
+        <v>-13.20185755253922</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-12.4872647361932</v>
       </c>
       <c r="E14">
-        <v>-27.12175293601259</v>
+        <v>-26.61291548261472</v>
       </c>
       <c r="F14">
-        <v>-5.168234075357791</v>
+        <v>-5.673751909855412</v>
       </c>
       <c r="G14">
-        <v>-12.31433008837047</v>
+        <v>-12.26515193438459</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-11.67334483285899</v>
       </c>
       <c r="E15">
-        <v>-28.37049775752373</v>
+        <v>-27.08039438290054</v>
       </c>
       <c r="F15">
-        <v>-5.207889679664609</v>
+        <v>-5.964652175798722</v>
       </c>
       <c r="G15">
-        <v>-11.69407620776924</v>
+        <v>-12.13106159786195</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.84386637456016</v>
       </c>
       <c r="E16">
-        <v>-29.83200840181124</v>
+        <v>-28.85896160636109</v>
       </c>
       <c r="F16">
-        <v>-4.568651808802676</v>
+        <v>-5.487935019161635</v>
       </c>
       <c r="G16">
-        <v>-11.53573612517143</v>
+        <v>-11.48444253258597</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.05800008335223</v>
       </c>
       <c r="E17">
-        <v>-29.37320605772412</v>
+        <v>-28.45657499146152</v>
       </c>
       <c r="F17">
-        <v>-4.869797322783811</v>
+        <v>-5.622869442138453</v>
       </c>
       <c r="G17">
-        <v>-11.54556513487753</v>
+        <v>-11.70653379063351</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.355631326877713</v>
       </c>
       <c r="E18">
-        <v>-30.16939556504171</v>
+        <v>-29.33116823351092</v>
       </c>
       <c r="F18">
-        <v>-4.593111841472539</v>
+        <v>-5.321027271171562</v>
       </c>
       <c r="G18">
-        <v>-11.43787970957612</v>
+        <v>-11.29310624259825</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.756378039037013</v>
       </c>
       <c r="E19">
-        <v>-30.56342488116012</v>
+        <v>-29.385537092447</v>
       </c>
       <c r="F19">
-        <v>-4.523743526794706</v>
+        <v>-5.327106659540709</v>
       </c>
       <c r="G19">
-        <v>-10.85845478711072</v>
+        <v>-11.5673452139804</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.285727170026625</v>
       </c>
       <c r="E20">
-        <v>-30.68461137407938</v>
+        <v>-30.47788653562923</v>
       </c>
       <c r="F20">
-        <v>-4.009865808468033</v>
+        <v>-5.084874635246674</v>
       </c>
       <c r="G20">
-        <v>-10.6263425077158</v>
+        <v>-11.39890796748782</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.943531128497694</v>
       </c>
       <c r="E21">
-        <v>-31.82586607230745</v>
+        <v>-30.67371812985393</v>
       </c>
       <c r="F21">
-        <v>-3.885261127004125</v>
+        <v>-4.732402648620679</v>
       </c>
       <c r="G21">
-        <v>-10.71120834261501</v>
+        <v>-11.18524204783771</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.714925528795608</v>
       </c>
       <c r="E22">
-        <v>-31.92641404493676</v>
+        <v>-31.04415183215538</v>
       </c>
       <c r="F22">
-        <v>-4.120349310816417</v>
+        <v>-4.669097983331338</v>
       </c>
       <c r="G22">
-        <v>-9.579107705641524</v>
+        <v>-11.81399078829272</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.589841876654191</v>
       </c>
       <c r="E23">
-        <v>-31.4558444611407</v>
+        <v>-29.95681540969964</v>
       </c>
       <c r="F23">
-        <v>-4.37494057676022</v>
+        <v>-4.62944237902452</v>
       </c>
       <c r="G23">
-        <v>-9.798315478524366</v>
+        <v>-11.64165702970042</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.539699906698051</v>
       </c>
       <c r="E24">
-        <v>-31.56704114039905</v>
+        <v>-31.2592452905717</v>
       </c>
       <c r="F24">
-        <v>-4.405924002727129</v>
+        <v>-4.338742577992686</v>
       </c>
       <c r="G24">
-        <v>-10.2798376377569</v>
+        <v>-11.36850060670961</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.535537160490364</v>
       </c>
       <c r="E25">
-        <v>-32.19029954654873</v>
+        <v>-30.93336045132072</v>
       </c>
       <c r="F25">
-        <v>-3.813024176010397</v>
+        <v>-4.259901882063841</v>
       </c>
       <c r="G25">
-        <v>-11.23924366667431</v>
+        <v>-11.65572684824232</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.55940897677895</v>
       </c>
       <c r="E26">
-        <v>-33.23848278273415</v>
+        <v>-31.41984082854272</v>
       </c>
       <c r="F26">
-        <v>-3.437650315799204</v>
+        <v>-4.108799384119183</v>
       </c>
       <c r="G26">
-        <v>-9.925635749419197</v>
+        <v>-12.28447227815178</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.58606574880167</v>
       </c>
       <c r="E27">
-        <v>-32.8019243029727</v>
+        <v>-32.00936436757226</v>
       </c>
       <c r="F27">
-        <v>-3.821833034971767</v>
+        <v>-4.013048396029588</v>
       </c>
       <c r="G27">
-        <v>-11.10996686336577</v>
+        <v>-12.47359712371927</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.601847633069555</v>
       </c>
       <c r="E28">
-        <v>-32.60157329168835</v>
+        <v>-31.64171567678553</v>
       </c>
       <c r="F28">
-        <v>-3.938414149772159</v>
+        <v>-4.245339183122626</v>
       </c>
       <c r="G28">
-        <v>-11.13261099485438</v>
+        <v>-12.09373850745221</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.606598575450087</v>
       </c>
       <c r="E29">
-        <v>-32.11647409903868</v>
+        <v>-31.34172918038442</v>
       </c>
       <c r="F29">
-        <v>-3.753581359552908</v>
+        <v>-4.168252969352909</v>
       </c>
       <c r="G29">
-        <v>-10.81815551626117</v>
+        <v>-12.38470235489875</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.597619954430022</v>
       </c>
       <c r="E30">
-        <v>-32.59465831187863</v>
+        <v>-30.91362536159529</v>
       </c>
       <c r="F30">
-        <v>-3.170791756987343</v>
+        <v>-4.056589043455536</v>
       </c>
       <c r="G30">
-        <v>-12.15866161602286</v>
+        <v>-12.34251938363736</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.58498303035449</v>
       </c>
       <c r="E31">
-        <v>-32.09354190666384</v>
+        <v>-31.44761622386877</v>
       </c>
       <c r="F31">
-        <v>-3.072665011186519</v>
+        <v>-3.843566910519018</v>
       </c>
       <c r="G31">
-        <v>-11.26663843101178</v>
+        <v>-12.70670918786705</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.583180073047819</v>
       </c>
       <c r="E32">
-        <v>-31.96329620149223</v>
+        <v>-30.94017127622825</v>
       </c>
       <c r="F32">
-        <v>-3.588925942531047</v>
+        <v>-4.054023589609066</v>
       </c>
       <c r="G32">
-        <v>-10.79359457890532</v>
+        <v>-12.85560097349577</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.596259234920611</v>
       </c>
       <c r="E33">
-        <v>-30.55350978732032</v>
+        <v>-30.74876173687204</v>
       </c>
       <c r="F33">
-        <v>-3.4657891281049</v>
+        <v>-4.181208635532694</v>
       </c>
       <c r="G33">
-        <v>-11.3230203320911</v>
+        <v>-13.18487445392276</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.632995420420719</v>
       </c>
       <c r="E34">
-        <v>-31.9337003596151</v>
+        <v>-30.22007371766155</v>
       </c>
       <c r="F34">
-        <v>-3.66179742295532</v>
+        <v>-3.818508796584333</v>
       </c>
       <c r="G34">
-        <v>-10.95013041418422</v>
+        <v>-12.37460519100398</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.695266740367717</v>
       </c>
       <c r="E35">
-        <v>-29.83707576422582</v>
+        <v>-30.80356532931287</v>
       </c>
       <c r="F35">
-        <v>-3.414388930761191</v>
+        <v>-4.195906358360565</v>
       </c>
       <c r="G35">
-        <v>-11.47268016428494</v>
+        <v>-12.0893288607939</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.770231685711013</v>
       </c>
       <c r="E36">
-        <v>-30.90090261387074</v>
+        <v>-30.26148208398768</v>
       </c>
       <c r="F36">
-        <v>-3.623600573644831</v>
+        <v>-3.870952736855569</v>
       </c>
       <c r="G36">
-        <v>-10.40630047735706</v>
+        <v>-12.43004689715015</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.851971307914242</v>
       </c>
       <c r="E37">
-        <v>-29.7870587688111</v>
+        <v>-29.0902262454588</v>
       </c>
       <c r="F37">
-        <v>-3.672810567575539</v>
+        <v>-4.091751582969569</v>
       </c>
       <c r="G37">
-        <v>-11.62806724026171</v>
+        <v>-11.90686814339697</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.928876870125001</v>
       </c>
       <c r="E38">
-        <v>-30.34652003314072</v>
+        <v>-29.98240808055399</v>
       </c>
       <c r="F38">
-        <v>-2.960879315280935</v>
+        <v>-3.634669218881038</v>
       </c>
       <c r="G38">
-        <v>-10.85383988662897</v>
+        <v>-12.29488394387279</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.981397520821799</v>
       </c>
       <c r="E39">
-        <v>-28.65809208480285</v>
+        <v>-29.39158713372125</v>
       </c>
       <c r="F39">
-        <v>-3.557722999202395</v>
+        <v>-3.86010526571591</v>
       </c>
       <c r="G39">
-        <v>-11.29349357642634</v>
+        <v>-11.78750973452409</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.003889704825076</v>
       </c>
       <c r="E40">
-        <v>-28.29489035549166</v>
+        <v>-28.42573608346929</v>
       </c>
       <c r="F40">
-        <v>-3.412920235356028</v>
+        <v>-3.920477510399341</v>
       </c>
       <c r="G40">
-        <v>-11.62311466413496</v>
+        <v>-12.39354813257969</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.987402519420289</v>
       </c>
       <c r="E41">
-        <v>-27.87851981285641</v>
+        <v>-28.45873054508917</v>
       </c>
       <c r="F41">
-        <v>-3.149232666962083</v>
+        <v>-4.070210717027171</v>
       </c>
       <c r="G41">
-        <v>-11.6251076125496</v>
+        <v>-11.36858668089363</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.920722180036484</v>
       </c>
       <c r="E42">
-        <v>-29.19458492896557</v>
+        <v>-27.98727111615061</v>
       </c>
       <c r="F42">
-        <v>-3.449672411916033</v>
+        <v>-3.875328173477156</v>
       </c>
       <c r="G42">
-        <v>-10.4810691483615</v>
+        <v>-11.15095141714195</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.808638526935443</v>
       </c>
       <c r="E43">
-        <v>-28.19782704361125</v>
+        <v>-28.05176564296785</v>
       </c>
       <c r="F43">
-        <v>-3.607487170925575</v>
+        <v>-4.126541357152343</v>
       </c>
       <c r="G43">
-        <v>-11.61023002089611</v>
+        <v>-11.96994727810224</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.652702647572089</v>
       </c>
       <c r="E44">
-        <v>-28.12338345939916</v>
+        <v>-27.2289147449301</v>
       </c>
       <c r="F44">
-        <v>-3.495497696638902</v>
+        <v>-3.833902348030556</v>
       </c>
       <c r="G44">
-        <v>-10.50773228213479</v>
+        <v>-11.51832596618041</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.453553145229924</v>
       </c>
       <c r="E45">
-        <v>-25.96600032824897</v>
+        <v>-26.16455579958929</v>
       </c>
       <c r="F45">
-        <v>-3.38338728071142</v>
+        <v>-3.971871080803828</v>
       </c>
       <c r="G45">
-        <v>-9.810124194462945</v>
+        <v>-11.58946958981934</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.223713992369875</v>
       </c>
       <c r="E46">
-        <v>-25.57286538574708</v>
+        <v>-25.34362044605678</v>
       </c>
       <c r="F46">
-        <v>-3.364588310872288</v>
+        <v>-3.833256221456372</v>
       </c>
       <c r="G46">
-        <v>-9.699962481098158</v>
+        <v>-11.23927346158416</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.969545372610429</v>
       </c>
       <c r="E47">
-        <v>-24.32735842315143</v>
+        <v>-25.32891649095388</v>
       </c>
       <c r="F47">
-        <v>-3.38863664494296</v>
+        <v>-4.159331452424759</v>
       </c>
       <c r="G47">
-        <v>-10.52363614290545</v>
+        <v>-11.70575912297732</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.696523042755793</v>
       </c>
       <c r="E48">
-        <v>-24.33028381736039</v>
+        <v>-25.61988453136872</v>
       </c>
       <c r="F48">
-        <v>-3.112006664247676</v>
+        <v>-3.895673705257315</v>
       </c>
       <c r="G48">
-        <v>-10.9494881683496</v>
+        <v>-11.68821323161919</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.417321044232918</v>
       </c>
       <c r="E49">
-        <v>-24.81148852236345</v>
+        <v>-25.29643827537086</v>
       </c>
       <c r="F49">
-        <v>-3.798313199304081</v>
+        <v>-4.128368735642919</v>
       </c>
       <c r="G49">
-        <v>-10.18692717719725</v>
+        <v>-11.72405650817288</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.136359697170918</v>
       </c>
       <c r="E50">
-        <v>-23.11856379933597</v>
+        <v>-24.24747161318212</v>
       </c>
       <c r="F50">
-        <v>-3.438995584461351</v>
+        <v>-4.384248112898074</v>
       </c>
       <c r="G50">
-        <v>-10.87519290535727</v>
+        <v>-11.7443236679643</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.858151987756028</v>
       </c>
       <c r="E51">
-        <v>-23.82355210437608</v>
+        <v>-23.74378303473097</v>
       </c>
       <c r="F51">
-        <v>-3.673556098238059</v>
+        <v>-4.249939935677774</v>
       </c>
       <c r="G51">
-        <v>-10.49287455375454</v>
+        <v>-11.90947685328192</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.592288263772201</v>
       </c>
       <c r="E52">
-        <v>-22.87515379294967</v>
+        <v>-23.776274835736</v>
       </c>
       <c r="F52">
-        <v>-3.127177384862546</v>
+        <v>-4.000443957628591</v>
       </c>
       <c r="G52">
-        <v>-10.14671398053173</v>
+        <v>-10.88231057826671</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.340671876238169</v>
       </c>
       <c r="E53">
-        <v>-22.29612499243292</v>
+        <v>-22.27534835368572</v>
       </c>
       <c r="F53">
-        <v>-3.24559084835793</v>
+        <v>-4.395151084653722</v>
       </c>
       <c r="G53">
-        <v>-11.34903790948424</v>
+        <v>-11.15068326295326</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.107686933895321</v>
       </c>
       <c r="E54">
-        <v>-22.86341598832179</v>
+        <v>-23.34290440167596</v>
       </c>
       <c r="F54">
-        <v>-3.319003252696231</v>
+        <v>-4.378470250263549</v>
       </c>
       <c r="G54">
-        <v>-11.08095324225959</v>
+        <v>-11.33755031646296</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.899908617447553</v>
       </c>
       <c r="E55">
-        <v>-21.17654130656856</v>
+        <v>-22.09516942986853</v>
       </c>
       <c r="F55">
-        <v>-3.881642818188697</v>
+        <v>-4.821438890543181</v>
       </c>
       <c r="G55">
-        <v>-11.25588577910022</v>
+        <v>-11.69288110082956</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.715472993806799</v>
       </c>
       <c r="E56">
-        <v>-21.02019574145374</v>
+        <v>-22.2470544480858</v>
       </c>
       <c r="F56">
-        <v>-3.230748161234569</v>
+        <v>-4.599162236982587</v>
       </c>
       <c r="G56">
-        <v>-11.57927310955839</v>
+        <v>-11.61271624059611</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.555906262301434</v>
       </c>
       <c r="E57">
-        <v>-21.99390822258302</v>
+        <v>-21.80234924358455</v>
       </c>
       <c r="F57">
-        <v>-3.850898790401196</v>
+        <v>-4.291631667060673</v>
       </c>
       <c r="G57">
-        <v>-12.58457985237779</v>
+        <v>-11.56500465828413</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.421574372235935</v>
       </c>
       <c r="E58">
-        <v>-20.99458722094036</v>
+        <v>-22.07253158830419</v>
       </c>
       <c r="F58">
-        <v>-3.635786686507415</v>
+        <v>-4.019115358887692</v>
       </c>
       <c r="G58">
-        <v>-11.70981454126293</v>
+        <v>-11.23831009283223</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.304684099058112</v>
       </c>
       <c r="E59">
-        <v>-20.06848258705372</v>
+        <v>-20.40306888911044</v>
       </c>
       <c r="F59">
-        <v>-3.402960774072169</v>
+        <v>-4.263046364724868</v>
       </c>
       <c r="G59">
-        <v>-11.98087869947292</v>
+        <v>-11.65888510868678</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.20370275118364</v>
       </c>
       <c r="E60">
-        <v>-21.15550201632892</v>
+        <v>-20.74614607993155</v>
       </c>
       <c r="F60">
-        <v>-3.532050236654833</v>
+        <v>-4.15210311846793</v>
       </c>
       <c r="G60">
-        <v>-11.09791647760282</v>
+        <v>-11.86735016129469</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.116319872024375</v>
       </c>
       <c r="E61">
-        <v>-20.69951638307457</v>
+        <v>-20.27204202217251</v>
       </c>
       <c r="F61">
-        <v>-3.581752280822804</v>
+        <v>-4.112194033735856</v>
       </c>
       <c r="G61">
-        <v>-11.6491918313478</v>
+        <v>-12.23750887913168</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.034709605001229</v>
       </c>
       <c r="E62">
-        <v>-19.3853351121526</v>
+        <v>-19.77058145293313</v>
       </c>
       <c r="F62">
-        <v>-3.545080455900869</v>
+        <v>-4.160354486167216</v>
       </c>
       <c r="G62">
-        <v>-11.78719192215232</v>
+        <v>-12.44098162906637</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.959018374018756</v>
       </c>
       <c r="E63">
-        <v>-20.49914046518317</v>
+        <v>-20.34992724663043</v>
       </c>
       <c r="F63">
-        <v>-3.774671593628183</v>
+        <v>-4.432386199409559</v>
       </c>
       <c r="G63">
-        <v>-12.04670227643025</v>
+        <v>-12.39239606273202</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.887527444736948</v>
       </c>
       <c r="E64">
-        <v>-19.31709100885701</v>
+        <v>-20.09300427380525</v>
       </c>
       <c r="F64">
-        <v>-3.771505573414683</v>
+        <v>-4.197976448500161</v>
       </c>
       <c r="G64">
-        <v>-11.66828374747277</v>
+        <v>-12.21564934693587</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.815110270023876</v>
       </c>
       <c r="E65">
-        <v>-19.02778491840298</v>
+        <v>-19.44870657741594</v>
       </c>
       <c r="F65">
-        <v>-3.566695046542117</v>
+        <v>-4.510604791418903</v>
       </c>
       <c r="G65">
-        <v>-12.0752755949797</v>
+        <v>-12.40982939554182</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.745284600658886</v>
       </c>
       <c r="E66">
-        <v>-20.18782599105186</v>
+        <v>-20.74539435324628</v>
       </c>
       <c r="F66">
-        <v>-3.772238678566161</v>
+        <v>-4.165257592824386</v>
       </c>
       <c r="G66">
-        <v>-11.13951017175822</v>
+        <v>-12.62174403660165</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.678818018106131</v>
       </c>
       <c r="E67">
-        <v>-20.00880182810663</v>
+        <v>-18.7546228377863</v>
       </c>
       <c r="F67">
-        <v>-3.957842678837418</v>
+        <v>-4.090835408622073</v>
       </c>
       <c r="G67">
-        <v>-12.51111553631583</v>
+        <v>-12.54066546579936</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.613670837555638</v>
       </c>
       <c r="E68">
-        <v>-19.42960547405158</v>
+        <v>-18.94957817229051</v>
       </c>
       <c r="F68">
-        <v>-3.703598498835388</v>
+        <v>-4.356665135119657</v>
       </c>
       <c r="G68">
-        <v>-12.68092996975274</v>
+        <v>-12.29378153220821</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.554406733781932</v>
       </c>
       <c r="E69">
-        <v>-19.06119147115756</v>
+        <v>-20.05192195760767</v>
       </c>
       <c r="F69">
-        <v>-3.492750001963816</v>
+        <v>-4.304483787315108</v>
       </c>
       <c r="G69">
-        <v>-11.48192320743058</v>
+        <v>-12.74746531400101</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.501940908112577</v>
       </c>
       <c r="E70">
-        <v>-19.52727107297501</v>
+        <v>-19.23538828081062</v>
       </c>
       <c r="F70">
-        <v>-3.523407879541426</v>
+        <v>-4.438365355322967</v>
       </c>
       <c r="G70">
-        <v>-12.72543032289162</v>
+        <v>-12.92193437446614</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.456711249403646</v>
       </c>
       <c r="E71">
-        <v>-19.05555352101801</v>
+        <v>-20.13930792053368</v>
       </c>
       <c r="F71">
-        <v>-3.971301992398105</v>
+        <v>-4.615575508701657</v>
       </c>
       <c r="G71">
-        <v>-12.3835171795957</v>
+        <v>-12.58970457687258</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.423309938906284</v>
       </c>
       <c r="E72">
-        <v>-20.22409453937929</v>
+        <v>-19.43087797524774</v>
       </c>
       <c r="F72">
-        <v>-3.690231134056412</v>
+        <v>-4.594860525059849</v>
       </c>
       <c r="G72">
-        <v>-12.68814033793727</v>
+        <v>-11.86718463401773</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.398975290426163</v>
       </c>
       <c r="E73">
-        <v>-18.92804074991003</v>
+        <v>-19.68758810979456</v>
       </c>
       <c r="F73">
-        <v>-4.014554367967878</v>
+        <v>-4.703096666644438</v>
       </c>
       <c r="G73">
-        <v>-11.42324047720146</v>
+        <v>-12.11030116678518</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.379196944260951</v>
       </c>
       <c r="E74">
-        <v>-19.42875412093814</v>
+        <v>-19.5545415434492</v>
       </c>
       <c r="F74">
-        <v>-3.615939003536339</v>
+        <v>-4.794725698537703</v>
       </c>
       <c r="G74">
-        <v>-12.18636426109548</v>
+        <v>-12.17228451091696</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.36410333964963</v>
       </c>
       <c r="E75">
-        <v>-19.5380669550093</v>
+        <v>-20.49433122578703</v>
       </c>
       <c r="F75">
-        <v>-4.22924648958844</v>
+        <v>-4.76220896450821</v>
       </c>
       <c r="G75">
-        <v>-10.78587438670774</v>
+        <v>-12.14117862502997</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.350195577895239</v>
       </c>
       <c r="E76">
-        <v>-21.4345058284155</v>
+        <v>-19.91218683515298</v>
       </c>
       <c r="F76">
-        <v>-4.264224303171649</v>
+        <v>-4.513922402867115</v>
       </c>
       <c r="G76">
-        <v>-11.64411345449056</v>
+        <v>-12.37944851912793</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.334834294291057</v>
       </c>
       <c r="E77">
-        <v>-20.72164703555005</v>
+        <v>-19.61299508594021</v>
       </c>
       <c r="F77">
-        <v>-4.354244645568676</v>
+        <v>-5.073487896927793</v>
       </c>
       <c r="G77">
-        <v>-12.05555136465672</v>
+        <v>-11.74652849129345</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.317691912694066</v>
       </c>
       <c r="E78">
-        <v>-20.5599669280542</v>
+        <v>-20.61924918128861</v>
       </c>
       <c r="F78">
-        <v>-4.03651355944869</v>
+        <v>-5.0124463313829</v>
       </c>
       <c r="G78">
-        <v>-11.55172274958058</v>
+        <v>-11.6520753165125</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.294536810498963</v>
       </c>
       <c r="E79">
-        <v>-21.50672140341582</v>
+        <v>-20.76818616292688</v>
       </c>
       <c r="F79">
-        <v>-4.708162961679959</v>
+        <v>-5.150790314589639</v>
       </c>
       <c r="G79">
-        <v>-11.74784277787254</v>
+        <v>-12.2566968010773</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.263317576918026</v>
       </c>
       <c r="E80">
-        <v>-21.2720332379683</v>
+        <v>-21.72771093499013</v>
       </c>
       <c r="F80">
-        <v>-4.479598999532118</v>
+        <v>-5.330417644049698</v>
       </c>
       <c r="G80">
-        <v>-10.75601988703459</v>
+        <v>-12.36253825251334</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.223939324315455</v>
       </c>
       <c r="E81">
-        <v>-22.13202667981696</v>
+        <v>-21.88228586676795</v>
       </c>
       <c r="F81">
-        <v>-4.790387538449242</v>
+        <v>-5.365480779475395</v>
       </c>
       <c r="G81">
-        <v>-11.88576010503858</v>
+        <v>-11.70843735431859</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.172972515385302</v>
       </c>
       <c r="E82">
-        <v>-23.4950747137557</v>
+        <v>-21.79710527068367</v>
       </c>
       <c r="F82">
-        <v>-4.692299725916349</v>
+        <v>-5.423842576472232</v>
       </c>
       <c r="G82">
-        <v>-11.317869123232</v>
+        <v>-10.58694370525293</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.110954393163637</v>
       </c>
       <c r="E83">
-        <v>-23.28160697750813</v>
+        <v>-23.69912775254133</v>
       </c>
       <c r="F83">
-        <v>-4.306682274402138</v>
+        <v>-5.94229619633197</v>
       </c>
       <c r="G83">
-        <v>-11.09704580412599</v>
+        <v>-11.4379459204869</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.04071358244831</v>
       </c>
       <c r="E84">
-        <v>-24.88906581058885</v>
+        <v>-24.01558204467134</v>
       </c>
       <c r="F84">
-        <v>-5.282261333455351</v>
+        <v>-5.894197871455819</v>
       </c>
       <c r="G84">
-        <v>-10.84617266316002</v>
+        <v>-11.31755462140577</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.963602060886405</v>
       </c>
       <c r="E85">
-        <v>-23.82536349397915</v>
+        <v>-24.53368475588891</v>
       </c>
       <c r="F85">
-        <v>-5.005936191964298</v>
+        <v>-5.980611502181058</v>
       </c>
       <c r="G85">
-        <v>-10.78263005207925</v>
+        <v>-10.6496851643132</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.890040822738002</v>
       </c>
       <c r="E86">
-        <v>-25.43198908784246</v>
+        <v>-25.86145144883389</v>
       </c>
       <c r="F86">
-        <v>-4.760179464371352</v>
+        <v>-5.952248202309203</v>
       </c>
       <c r="G86">
-        <v>-10.2714751997247</v>
+        <v>-10.22559765964148</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.834187932272455</v>
       </c>
       <c r="E87">
-        <v>-27.14723918772776</v>
+        <v>-26.43769070936192</v>
       </c>
       <c r="F87">
-        <v>-5.556436033168738</v>
+        <v>-6.036226432870211</v>
       </c>
       <c r="G87">
-        <v>-10.14146676585198</v>
+        <v>-10.68424394919765</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.809309300049815</v>
       </c>
       <c r="E88">
-        <v>-27.31251490358571</v>
+        <v>-27.76417131568872</v>
       </c>
       <c r="F88">
-        <v>-5.576250581443702</v>
+        <v>-6.471564152635255</v>
       </c>
       <c r="G88">
-        <v>-11.847860979705</v>
+        <v>-10.54890884755224</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.839230746072512</v>
       </c>
       <c r="E89">
-        <v>-28.82332251592072</v>
+        <v>-27.86979797191763</v>
       </c>
       <c r="F89">
-        <v>-5.176071259355678</v>
+        <v>-6.600662727259349</v>
       </c>
       <c r="G89">
-        <v>-10.19432293593199</v>
+        <v>-10.81625857366717</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.944198358329541</v>
       </c>
       <c r="E90">
-        <v>-30.2241810435865</v>
+        <v>-30.4674778381226</v>
       </c>
       <c r="F90">
-        <v>-5.184526405436052</v>
+        <v>-6.838712324536649</v>
       </c>
       <c r="G90">
-        <v>-10.76046263914829</v>
+        <v>-10.29282159736192</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.133939804322028</v>
       </c>
       <c r="E91">
-        <v>-30.81604580367801</v>
+        <v>-31.71591245916421</v>
       </c>
       <c r="F91">
-        <v>-5.584412485463485</v>
+        <v>-6.980098901213871</v>
       </c>
       <c r="G91">
-        <v>-10.92382812987471</v>
+        <v>-11.16304815054244</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.421109834444386</v>
       </c>
       <c r="E92">
-        <v>-31.77379314969325</v>
+        <v>-32.54444206360758</v>
       </c>
       <c r="F92">
-        <v>-5.970941141120776</v>
+        <v>-6.983037948759004</v>
       </c>
       <c r="G92">
-        <v>-10.86246054721324</v>
+        <v>-10.69918444121638</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.804908928882031</v>
       </c>
       <c r="E93">
-        <v>-34.50267196484844</v>
+        <v>-33.92970226255394</v>
       </c>
       <c r="F93">
-        <v>-6.149455973158876</v>
+        <v>-7.386271875644852</v>
       </c>
       <c r="G93">
-        <v>-10.82695163575901</v>
+        <v>-10.9139395303489</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.271466309326132</v>
       </c>
       <c r="E94">
-        <v>-35.24028566087681</v>
+        <v>-36.00539851531676</v>
       </c>
       <c r="F94">
-        <v>-6.218747249668248</v>
+        <v>-7.379863211233094</v>
       </c>
       <c r="G94">
-        <v>-11.50257107995902</v>
+        <v>-11.43665480772659</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.808964706704737</v>
       </c>
       <c r="E95">
-        <v>-36.78202501492122</v>
+        <v>-38.49699887789205</v>
       </c>
       <c r="F95">
-        <v>-6.272736095145707</v>
+        <v>-7.796708457098041</v>
       </c>
       <c r="G95">
-        <v>-11.57703518077384</v>
+        <v>-11.5409767187601</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.398830190032526</v>
       </c>
       <c r="E96">
-        <v>-38.29643729256635</v>
+        <v>-39.25222154509925</v>
       </c>
       <c r="F96">
-        <v>-6.736591191119526</v>
+        <v>-7.882580335541848</v>
       </c>
       <c r="G96">
-        <v>-11.32136505932147</v>
+        <v>-11.8430639992186</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.009616537912709</v>
       </c>
       <c r="E97">
-        <v>-41.20919705903999</v>
+        <v>-41.17821776835352</v>
       </c>
       <c r="F97">
-        <v>-6.503263288038184</v>
+        <v>-8.042446960608125</v>
       </c>
       <c r="G97">
-        <v>-11.27193861442015</v>
+        <v>-12.72857865169947</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.634702983636328</v>
       </c>
       <c r="E98">
-        <v>-43.77271185309409</v>
+        <v>-43.33555335052663</v>
       </c>
       <c r="F98">
-        <v>-7.145884211373151</v>
+        <v>-8.251861967689154</v>
       </c>
       <c r="G98">
-        <v>-12.54728986742344</v>
+        <v>-12.63935613887057</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.233135435184292</v>
       </c>
       <c r="E99">
-        <v>-45.51442182660621</v>
+        <v>-45.3506450356448</v>
       </c>
       <c r="F99">
-        <v>-6.998972424119255</v>
+        <v>-8.579432816003294</v>
       </c>
       <c r="G99">
-        <v>-12.89663849600057</v>
+        <v>-12.87961567083764</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.809667949825743</v>
       </c>
       <c r="E100">
-        <v>-46.74928687528383</v>
+        <v>-47.18483324110456</v>
       </c>
       <c r="F100">
-        <v>-7.384580763592036</v>
+        <v>-8.939289283841545</v>
       </c>
       <c r="G100">
-        <v>-13.50708985126002</v>
+        <v>-13.34309204633561</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.310959808458481</v>
       </c>
       <c r="E101">
-        <v>-49.01807046702271</v>
+        <v>-49.07775575444381</v>
       </c>
       <c r="F101">
-        <v>-7.314455321108045</v>
+        <v>-8.66711219212001</v>
       </c>
       <c r="G101">
-        <v>-13.35080892798765</v>
+        <v>-13.69998706346951</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.795442223741077</v>
       </c>
       <c r="E102">
-        <v>-51.1556720915889</v>
+        <v>-51.51263471583602</v>
       </c>
       <c r="F102">
-        <v>-7.485115159249097</v>
+        <v>-8.737754535863349</v>
       </c>
       <c r="G102">
-        <v>-13.51079766226401</v>
+        <v>-14.37200463412278</v>
       </c>
     </row>
   </sheetData>
